--- a/diseases/d127/2010-2014.xlsx
+++ b/diseases/d127/2010-2014.xlsx
@@ -5492,6 +5492,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11401,6 +11406,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11549,6 +11559,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11697,6 +11712,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11845,6 +11865,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11993,6 +12018,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12141,6 +12171,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12289,6 +12324,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12437,6 +12477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12585,6 +12630,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12733,6 +12783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12881,6 +12936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17745,6 +17805,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23654,6 +23719,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23802,6 +23872,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23950,6 +24025,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24098,6 +24178,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24246,6 +24331,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24394,6 +24484,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24542,6 +24637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24690,6 +24790,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24838,6 +24943,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24986,6 +25096,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25134,6 +25249,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30391,6 +30511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36693,6 +36818,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36841,6 +36971,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36989,6 +37124,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37137,6 +37277,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37285,6 +37430,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37433,6 +37583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37581,6 +37736,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37729,6 +37889,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37877,6 +38042,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38025,6 +38195,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38173,6 +38348,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43037,6 +43217,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48946,6 +49131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49094,6 +49284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49242,6 +49437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49390,6 +49590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49538,6 +49743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49686,6 +49896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49834,6 +50049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49982,6 +50202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50130,6 +50355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50278,6 +50508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50426,6 +50661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55683,6 +55923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61831,6 +62076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62218,6 +62468,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62605,6 +62860,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62992,6 +63252,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63379,6 +63644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63766,6 +64036,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64153,6 +64428,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64540,6 +64820,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64927,6 +65212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65314,6 +65604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65699,6 +65994,11 @@
       <c r="S343" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO343" t="inlineStr">

--- a/diseases/d127/2010-2014.xlsx
+++ b/diseases/d127/2010-2014.xlsx
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         </is>
       </c>
       <c r="AT142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         </is>
       </c>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         </is>
       </c>
       <c r="AT211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         </is>
       </c>
       <c r="AT212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         </is>
       </c>
       <c r="AT276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
@@ -53041,7 +53041,7 @@
         </is>
       </c>
       <c r="AT277" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>

--- a/diseases/d127/2010-2014.xlsx
+++ b/diseases/d127/2010-2014.xlsx
@@ -5487,6 +5487,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5499,12 +5504,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -11386,6 +11401,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11398,12 +11418,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -11524,6 +11554,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11536,12 +11571,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -11662,6 +11707,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11674,12 +11724,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -11800,6 +11860,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11812,12 +11877,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -11938,6 +12013,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11950,12 +12030,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -12076,6 +12166,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12088,12 +12183,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -12214,6 +12319,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12226,12 +12336,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -12352,6 +12472,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12364,12 +12489,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -12490,6 +12625,11 @@
       <c r="R64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12502,12 +12642,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -12628,6 +12778,11 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12640,12 +12795,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -12766,6 +12931,11 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12778,12 +12948,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -17620,6 +17800,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17632,12 +17817,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -23519,6 +23714,11 @@
       <c r="R121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23531,12 +23731,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -23657,6 +23867,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23669,12 +23884,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -23795,6 +24020,11 @@
       <c r="R123" t="n">
         <v>0</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23807,12 +24037,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -23933,6 +24173,11 @@
       <c r="R124" t="n">
         <v>0</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23945,12 +24190,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -24071,6 +24326,11 @@
       <c r="R125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24083,12 +24343,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -24209,6 +24479,11 @@
       <c r="R126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24221,12 +24496,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -24347,6 +24632,11 @@
       <c r="R127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24359,12 +24649,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -24485,6 +24785,11 @@
       <c r="R128" t="n">
         <v>0</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24497,12 +24802,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -24623,6 +24938,11 @@
       <c r="R129" t="n">
         <v>0</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24635,12 +24955,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -24761,6 +25091,11 @@
       <c r="R130" t="n">
         <v>0</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24773,12 +25108,22 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -24899,6 +25244,11 @@
       <c r="R131" t="n">
         <v>0</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24911,12 +25261,22 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -30146,6 +30506,11 @@
       <c r="R158" t="n">
         <v>0</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30158,12 +30523,22 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -36045,6 +36420,11 @@
       <c r="R188" t="n">
         <v>0</v>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36057,12 +36437,22 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -36183,6 +36573,11 @@
       <c r="R189" t="n">
         <v>0</v>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36195,12 +36590,22 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -36321,6 +36726,11 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36333,12 +36743,22 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -36459,6 +36879,11 @@
       <c r="R191" t="n">
         <v>0</v>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36471,12 +36896,22 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -36597,6 +37032,11 @@
       <c r="R192" t="n">
         <v>0</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36609,12 +37049,22 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -36735,6 +37185,11 @@
       <c r="R193" t="n">
         <v>0</v>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36747,12 +37202,22 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -36873,6 +37338,11 @@
       <c r="R194" t="n">
         <v>0</v>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36885,12 +37355,22 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -37011,6 +37491,11 @@
       <c r="R195" t="n">
         <v>0</v>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37023,12 +37508,22 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -37149,6 +37644,11 @@
       <c r="R196" t="n">
         <v>0</v>
       </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37161,12 +37661,22 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
         <v>0</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -37287,6 +37797,11 @@
       <c r="R197" t="n">
         <v>0</v>
       </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37299,12 +37814,22 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -37425,6 +37950,11 @@
       <c r="R198" t="n">
         <v>0</v>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37437,12 +37967,22 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -42279,6 +42819,11 @@
       <c r="R223" t="n">
         <v>0</v>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42291,12 +42836,22 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -47785,6 +48340,11 @@
       <c r="R251" t="n">
         <v>0</v>
       </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47797,12 +48357,22 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
         <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
@@ -47923,6 +48493,11 @@
       <c r="R252" t="n">
         <v>0</v>
       </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47935,12 +48510,22 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
@@ -48061,6 +48646,11 @@
       <c r="R253" t="n">
         <v>0</v>
       </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48073,12 +48663,22 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
         <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
@@ -48199,6 +48799,11 @@
       <c r="R254" t="n">
         <v>0</v>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48211,12 +48816,22 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
         <v>0</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
@@ -48337,6 +48952,11 @@
       <c r="R255" t="n">
         <v>0</v>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48349,12 +48969,22 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
         <v>0</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
@@ -48475,6 +49105,11 @@
       <c r="R256" t="n">
         <v>0</v>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48487,12 +49122,22 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
         <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
@@ -48613,6 +49258,11 @@
       <c r="R257" t="n">
         <v>0</v>
       </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48625,12 +49275,22 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
         <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
@@ -48751,6 +49411,11 @@
       <c r="R258" t="n">
         <v>0</v>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48763,12 +49428,22 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
         <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
@@ -48889,6 +49564,11 @@
       <c r="R259" t="n">
         <v>0</v>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48901,12 +49581,22 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -49027,6 +49717,11 @@
       <c r="R260" t="n">
         <v>0</v>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49039,12 +49734,22 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
         <v>0</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
@@ -49165,6 +49870,11 @@
       <c r="R261" t="n">
         <v>0</v>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49177,12 +49887,22 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
         <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
@@ -54412,6 +55132,11 @@
       <c r="R288" t="n">
         <v>0</v>
       </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54424,12 +55149,22 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr"/>
       <c r="AT288" t="n">
         <v>0</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
@@ -60157,6 +60892,11 @@
       <c r="R317" t="n">
         <v>0</v>
       </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA317" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60169,12 +60909,22 @@
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS317" t="inlineStr"/>
       <c r="AT317" t="n">
         <v>0</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
@@ -60534,6 +61284,11 @@
       <c r="R319" t="n">
         <v>0</v>
       </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA319" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60546,12 +61301,22 @@
       </c>
       <c r="AP319" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS319" t="inlineStr"/>
       <c r="AT319" t="n">
         <v>0</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV319" t="inlineStr">
         <is>
@@ -60911,6 +61676,11 @@
       <c r="R321" t="n">
         <v>0</v>
       </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA321" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60923,12 +61693,22 @@
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS321" t="inlineStr"/>
       <c r="AT321" t="n">
         <v>0</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV321" t="inlineStr">
         <is>
@@ -61288,6 +62068,11 @@
       <c r="R323" t="n">
         <v>0</v>
       </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA323" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61300,12 +62085,22 @@
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS323" t="inlineStr"/>
       <c r="AT323" t="n">
         <v>0</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV323" t="inlineStr">
         <is>
@@ -61665,6 +62460,11 @@
       <c r="R325" t="n">
         <v>0</v>
       </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA325" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61677,12 +62477,22 @@
       </c>
       <c r="AP325" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR325" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS325" t="inlineStr"/>
       <c r="AT325" t="n">
         <v>0</v>
+      </c>
+      <c r="AU325" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV325" t="inlineStr">
         <is>
@@ -62042,6 +62852,11 @@
       <c r="R327" t="n">
         <v>0</v>
       </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA327" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62054,12 +62869,22 @@
       </c>
       <c r="AP327" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR327" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS327" t="inlineStr"/>
       <c r="AT327" t="n">
         <v>0</v>
+      </c>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV327" t="inlineStr">
         <is>
@@ -62419,6 +63244,11 @@
       <c r="R329" t="n">
         <v>0</v>
       </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA329" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62431,12 +63261,22 @@
       </c>
       <c r="AP329" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR329" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS329" t="inlineStr"/>
       <c r="AT329" t="n">
         <v>0</v>
+      </c>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV329" t="inlineStr">
         <is>
@@ -62796,6 +63636,11 @@
       <c r="R331" t="n">
         <v>0</v>
       </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA331" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62808,12 +63653,22 @@
       </c>
       <c r="AP331" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR331" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS331" t="inlineStr"/>
       <c r="AT331" t="n">
         <v>0</v>
+      </c>
+      <c r="AU331" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV331" t="inlineStr">
         <is>
@@ -63173,6 +64028,11 @@
       <c r="R333" t="n">
         <v>0</v>
       </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA333" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63185,12 +64045,22 @@
       </c>
       <c r="AP333" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR333" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS333" t="inlineStr"/>
       <c r="AT333" t="n">
         <v>0</v>
+      </c>
+      <c r="AU333" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV333" t="inlineStr">
         <is>
@@ -63550,6 +64420,11 @@
       <c r="R335" t="n">
         <v>0</v>
       </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA335" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63562,12 +64437,22 @@
       </c>
       <c r="AP335" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR335" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS335" t="inlineStr"/>
       <c r="AT335" t="n">
         <v>0</v>
+      </c>
+      <c r="AU335" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV335" t="inlineStr">
         <is>
@@ -63927,6 +64812,11 @@
       <c r="R337" t="n">
         <v>0</v>
       </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA337" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63939,12 +64829,22 @@
       </c>
       <c r="AP337" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR337" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS337" t="inlineStr"/>
       <c r="AT337" t="n">
         <v>0</v>
+      </c>
+      <c r="AU337" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV337" t="inlineStr">
         <is>
